--- a/log-processor/log_analysis.xlsx
+++ b/log-processor/log_analysis.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,7 +52,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,7 +142,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Web cache retrieval took value ms (seconds)</a:t>
+              <a:t>DB retrieval took value millis (seconds)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -155,7 +156,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'server-a'!C1</f>
+              <f>'server-a'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -173,12 +174,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'server-a'!$D$2:$D$6</f>
+              <f>'server-a'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'server-a'!$C$2:$C$6</f>
+              <f>'server-a'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -246,7 +247,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Web cache retrieval took value ms (seconds)</a:t>
+              <a:t>DB retrieval took value millis (seconds)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -260,7 +261,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'server-b'!C1</f>
+              <f>'server-b'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -278,12 +279,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'server-b'!$D$2:$D$6</f>
+              <f>'server-b'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'server-b'!$C$2:$C$6</f>
+              <f>'server-b'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -681,125 +682,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col hidden="1" width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>23:58:10</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="1" t="n">
+        <v>46174.99872685185</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.12</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>46174.99872685185</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>23:59:45</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="1" t="n">
+        <v>46174.99982638889</v>
+      </c>
+      <c r="B3" t="n">
         <v>0.095</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>46174.99982638889</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00:02:30</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="A4" s="1" t="n">
         <v>46175.00173611111</v>
       </c>
+      <c r="B4" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>08:15:00</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" s="1" t="n">
+        <v>46175.34375</v>
+      </c>
+      <c r="B5" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>46175.34375</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>12:30:22</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="A6" s="1" t="n">
         <v>46175.52108796296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -814,125 +753,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col hidden="1" width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>14:00:01</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="1" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>46174.58334490741</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>18:22:10</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="1" t="n">
+        <v>46174.76539351852</v>
+      </c>
+      <c r="B3" t="n">
         <v>0.175</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>46174.76539351852</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>23:50:00</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="A4" s="1" t="n">
+        <v>46174.99305555555</v>
+      </c>
+      <c r="B4" t="n">
         <v>0.09</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>46174.99305555555</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00:05:12</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="A5" s="1" t="n">
         <v>46175.00361111111</v>
       </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06:00:00</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>46175.25</v>
+      </c>
+      <c r="B6" t="n">
         <v>0.11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46175.25</v>
       </c>
     </row>
   </sheetData>

--- a/log-processor/log_analysis.xlsx
+++ b/log-processor/log_analysis.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="server-a" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="server-b" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="server-a" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="server-b" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$E$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -127,270 +130,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>DB retrieval took value millis (seconds)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'server-a'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'server-a'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'server-a'!$B$2:$B$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="500"/>
-        <axId val="100"/>
-      </lineChart>
-      <dateAx>
-        <axId val="500"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <numFmt formatCode="yyyy-mm-dd hh:mm" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <majorTimeUnit val="days"/>
-      </dateAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Seconds</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>DB retrieval took value millis (seconds)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'server-b'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'server-b'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'server-b'!$B$2:$B$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="500"/>
-        <axId val="100"/>
-      </lineChart>
-      <dateAx>
-        <axId val="500"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <numFmt formatCode="yyyy-mm-dd hh:mm" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <majorTimeUnit val="days"/>
-      </dateAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Seconds</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8640000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8640000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -682,22 +421,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>server-a DateTime</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Seconds</t>
+          <t>server-a Seconds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>server-b DateTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>server-b Seconds</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
         </is>
       </c>
     </row>
@@ -708,6 +465,17 @@
       <c r="B2" t="n">
         <v>0.12</v>
       </c>
+      <c r="C2" s="1" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -716,6 +484,17 @@
       <c r="B3" t="n">
         <v>0.095</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <v>46174.76539351852</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -724,6 +503,17 @@
       <c r="B4" t="n">
         <v>2.1</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <v>46174.99305555555</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -732,6 +522,17 @@
       <c r="B5" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <v>46175.00361111111</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -740,10 +541,21 @@
       <c r="B6" t="n">
         <v>1.5</v>
       </c>
+      <c r="C6" s="1" t="n">
+        <v>46175.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -753,11 +565,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,6 +591,224 @@
           <t>Seconds</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>&gt;10s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>&gt;30s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>&gt;1min</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>&gt;2min</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>&gt;3min</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>&gt;4min</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>&gt;5min</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46174.99872685185</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46174.99982638889</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46175.00173611111</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46175.34375</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46175.52108796296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>&gt;10s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>&gt;30s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>&gt;1min</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>&gt;2min</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>&gt;3min</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>&gt;4min</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>&gt;5min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -779,6 +817,18 @@
       <c r="B2" t="n">
         <v>0.3</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -787,6 +837,18 @@
       <c r="B3" t="n">
         <v>0.175</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -795,6 +857,18 @@
       <c r="B4" t="n">
         <v>0.09</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -803,6 +877,18 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -811,9 +897,20 @@
       <c r="B6" t="n">
         <v>0.11</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/log-processor/log_analysis.xlsx
+++ b/log-processor/log_analysis.xlsx
@@ -12,7 +12,9 @@
     <sheet name="server-b" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'server-a'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'server-b'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,8 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,140 +426,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>server-a DateTime</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>server-a Seconds</t>
+          <t>DateTime</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>server-b DateTime</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>server-b Seconds</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46174.76539351852</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46174.99305555555</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>46174.99872685185</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C5" t="n">
         <v>0.12</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>46174.58334490741</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>46174.99982638889</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C6" t="n">
         <v>0.095</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>46174.76539351852</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>46175.00173611111</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C7" t="n">
         <v>2.1</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>46174.99305555555</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46175.00361111111</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46175.25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>46175.34375</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C10" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46175.00361111111</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>46175.52108796296</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C11" t="n">
         <v>1.5</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>46175.25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -565,19 +649,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,148 +668,79 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>&gt;10s</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>&gt;30s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>&gt;1min</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>&gt;2min</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>&gt;3min</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>&gt;4min</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>&gt;5min</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46174.99872685185</v>
       </c>
       <c r="B2" t="n">
         <v>0.12</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46174.99982638889</v>
       </c>
       <c r="B3" t="n">
         <v>0.095</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46175.00173611111</v>
       </c>
       <c r="B4" t="n">
         <v>2.1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46175.34375</v>
       </c>
       <c r="B5" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46175.52108796296</v>
       </c>
       <c r="B6" t="n">
         <v>1.5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -743,19 +751,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -769,148 +770,79 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>&gt;10s</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>&gt;30s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>&gt;1min</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>&gt;2min</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>&gt;3min</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>&gt;4min</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>&gt;5min</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46174.58334490741</v>
       </c>
       <c r="B2" t="n">
         <v>0.3</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46174.76539351852</v>
       </c>
       <c r="B3" t="n">
         <v>0.175</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46174.99305555555</v>
       </c>
       <c r="B4" t="n">
         <v>0.09</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46175.00361111111</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46175.25</v>
       </c>
       <c r="B6" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/log-processor/log_analysis.xlsx
+++ b/log-processor/log_analysis.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="server-a" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="server-b" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="server-a" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="server-b" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'server-a'!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'server-b'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'server-a'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'server-b'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,16 +35,139 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001E293B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000EA5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFFAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0006B6D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0014B8A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006D28D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD34D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +175,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -423,6 +636,410 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006D28D9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Log Analysis Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05 10:34:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Line pattern</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>DB retrieval took x millis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Min filter</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>none (all matching lines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Output file</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>log_analysis.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Log files</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>server-a.log, server-b.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;10s</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;30s</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;1min</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;2min</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;3min</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;4min</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>&gt;5min</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Avg (s)</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>Median (s)</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>P95 (s)</t>
+        </is>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>Max (s)</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>%&gt;1 min</t>
+        </is>
+      </c>
+      <c r="P9" s="14" t="inlineStr">
+        <is>
+          <t>%&gt;5 min</t>
+        </is>
+      </c>
+      <c r="Q9" s="14" t="inlineStr">
+        <is>
+          <t>First seen</t>
+        </is>
+      </c>
+      <c r="R9" s="14" t="inlineStr">
+        <is>
+          <t>Last seen</t>
+        </is>
+      </c>
+      <c r="S9" s="14" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="18" t="n">
+        <v>46174.99872685185</v>
+      </c>
+      <c r="R10" s="18" t="n">
+        <v>46175.52108796296</v>
+      </c>
+      <c r="S10" s="17" t="inlineStr">
+        <is>
+          <t>&lt;=10s: 5 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="21" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="R11" s="21" t="n">
+        <v>46175.25</v>
+      </c>
+      <c r="S11" s="20" t="inlineStr">
+        <is>
+          <t>&lt;=10s: 5 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>ALL SOURCES</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>3.145</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="25" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="R12" s="25" t="n">
+        <v>46175.52108796296</v>
+      </c>
+      <c r="S12" s="24" t="inlineStr">
+        <is>
+          <t>&lt;=10s: 10 times</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -451,7 +1068,7 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
@@ -463,13 +1080,13 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="27" t="n">
         <v>46174.58334490741</v>
       </c>
       <c r="C2" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -481,13 +1098,13 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="27" t="n">
         <v>46174.76539351852</v>
       </c>
       <c r="C3" t="n">
         <v>0.175</v>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -499,13 +1116,13 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="27" t="n">
         <v>46174.99305555555</v>
       </c>
       <c r="C4" t="n">
         <v>0.09</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -517,13 +1134,13 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="27" t="n">
         <v>46174.99872685185</v>
       </c>
       <c r="C5" t="n">
         <v>0.12</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -535,13 +1152,13 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="27" t="n">
         <v>46174.99982638889</v>
       </c>
       <c r="C6" t="n">
         <v>0.095</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -553,13 +1170,13 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="27" t="n">
         <v>46175.00173611111</v>
       </c>
       <c r="C7" t="n">
         <v>2.1</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -571,13 +1188,13 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="27" t="n">
         <v>46175.00361111111</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -589,13 +1206,13 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="27" t="n">
         <v>46175.25</v>
       </c>
       <c r="C9" t="n">
         <v>0.11</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -607,13 +1224,13 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="27" t="n">
         <v>46175.34375</v>
       </c>
       <c r="C10" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -625,13 +1242,13 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="27" t="n">
         <v>46175.52108796296</v>
       </c>
       <c r="C11" t="n">
         <v>1.5</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
@@ -639,108 +1256,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Seconds</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46174.99872685185</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46174.99982638889</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46175.00173611111</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46175.34375</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46175.52108796296</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -770,72 +1285,174 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="27" t="n">
+        <v>46174.99872685185</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="n">
+        <v>46174.99982638889</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="n">
+        <v>46175.00173611111</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="n">
+        <v>46175.34375</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
+        <v>46175.52108796296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="n">
         <v>46174.58334490741</v>
       </c>
       <c r="B2" t="n">
         <v>0.3</v>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="27" t="n">
         <v>46174.76539351852</v>
       </c>
       <c r="B3" t="n">
         <v>0.175</v>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="27" t="n">
         <v>46174.99305555555</v>
       </c>
       <c r="B4" t="n">
         <v>0.09</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="27" t="n">
         <v>46175.00361111111</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="27" t="n">
         <v>46175.25</v>
       </c>
       <c r="B6" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>&lt;=10s</t>
         </is>

--- a/log-processor/log_analysis.xlsx
+++ b/log-processor/log_analysis.xlsx
@@ -13,9 +13,9 @@
     <sheet name="server-b" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'server-a'!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'server-b'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'server-a'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'server-b'!$A$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,21 +37,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="00334155"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="001E293B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0064748B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -60,11 +51,21 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00475569"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00334155"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,72 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
+        <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003B82F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0F2FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000EA5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0006B6D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CCFBF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0014B8A6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0010B981"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006D28D9"/>
+        <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,22 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
+        <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F3FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCD34D"/>
+        <fgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,97 +108,64 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,42 +534,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006D28D9"/>
+    <tabColor rgb="0094A3B8"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Log Analysis Summary</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Generated</t>
@@ -679,359 +570,602 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 10:34:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+          <t>2026-06-05 11:15:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Start date</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Business hours</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>09:00 - 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Line pattern</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>DB retrieval took x millis</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Min filter</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>none (all matching lines)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Output file</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>log_analysis.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Log files</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>server-a.log, server-b.log</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9"/>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Performance summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>BH Y</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>BH N</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Avg (s)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Median (s)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P95 (s)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Max (s)</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>%&gt;1 min</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>%&gt;5 min</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>First seen</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Last seen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>46174.99872685185</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>46176.6044212963</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>46176.25</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>ALL SOURCES</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>3.145</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>46174.58334490741</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>46176.6044212963</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Bucket counts — business hours (09:00 - 16:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>&gt;10s</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>&gt;30s</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>&gt;1min</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>&gt;2min</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>&gt;3min</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>&gt;4min</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>&gt;5min</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>Avg (s)</t>
-        </is>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>Median (s)</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="inlineStr">
-        <is>
-          <t>P95 (s)</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>Max (s)</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>%&gt;1 min</t>
-        </is>
-      </c>
-      <c r="P9" s="14" t="inlineStr">
-        <is>
-          <t>%&gt;5 min</t>
-        </is>
-      </c>
-      <c r="Q9" s="14" t="inlineStr">
-        <is>
-          <t>First seen</t>
-        </is>
-      </c>
-      <c r="R9" s="14" t="inlineStr">
-        <is>
-          <t>Last seen</t>
-        </is>
-      </c>
-      <c r="S9" s="14" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>server-a</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="L10" s="17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="N10" s="17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="18" t="n">
-        <v>46174.99872685185</v>
-      </c>
-      <c r="R10" s="18" t="n">
-        <v>46175.52108796296</v>
-      </c>
-      <c r="S10" s="17" t="inlineStr">
-        <is>
-          <t>&lt;=10s: 5 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>server-b</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="L11" s="20" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N11" s="20" t="n">
+      <c r="B19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>ALL SOURCES</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="21" t="n">
-        <v>46174.58334490741</v>
-      </c>
-      <c r="R11" s="21" t="n">
-        <v>46175.25</v>
-      </c>
-      <c r="S11" s="20" t="inlineStr">
-        <is>
-          <t>&lt;=10s: 5 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="C20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Bucket counts — outside business hours (09:00 - 16:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;10s</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;30s</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;1min</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;2min</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;3min</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;4min</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>&gt;5min</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>ALL SOURCES</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="M12" s="24" t="n">
-        <v>3.145</v>
-      </c>
-      <c r="N12" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="25" t="n">
-        <v>46174.58334490741</v>
-      </c>
-      <c r="R12" s="25" t="n">
-        <v>46175.52108796296</v>
-      </c>
-      <c r="S12" s="24" t="inlineStr">
-        <is>
-          <t>&lt;=10s: 10 times</t>
-        </is>
+      <c r="B26" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A10:L10"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1043,13 +1177,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1068,9 +1203,14 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Bucket</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Business Hours</t>
         </is>
       </c>
     </row>
@@ -1080,15 +1220,20 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="16" t="n">
         <v>46174.58334490741</v>
       </c>
       <c r="C2" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1098,15 +1243,20 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B3" s="27" t="n">
+      <c r="B3" s="16" t="n">
         <v>46174.76539351852</v>
       </c>
       <c r="C3" t="n">
         <v>0.175</v>
       </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1116,15 +1266,20 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n">
+      <c r="B4" s="16" t="n">
         <v>46174.99305555555</v>
       </c>
       <c r="C4" t="n">
         <v>0.09</v>
       </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1134,15 +1289,20 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="16" t="n">
         <v>46174.99872685185</v>
       </c>
       <c r="C5" t="n">
         <v>0.12</v>
       </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1152,51 +1312,66 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>46174.99982638889</v>
+      <c r="B6" s="16" t="n">
+        <v>46175.42708333334</v>
       </c>
       <c r="C6" t="n">
         <v>0.095</v>
       </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>server-a</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n">
-        <v>46175.00173611111</v>
+          <t>server-b</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>46175.46194444445</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+        <v>4</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>server-b</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="n">
-        <v>46175.00361111111</v>
+          <t>server-a</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>46176.00173611111</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1206,15 +1381,20 @@
           <t>server-b</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>46175.25</v>
+      <c r="B9" s="16" t="n">
+        <v>46176.25</v>
       </c>
       <c r="C9" t="n">
         <v>0.11</v>
       </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1224,15 +1404,20 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
-        <v>46175.34375</v>
+      <c r="B10" s="16" t="n">
+        <v>46176.34375</v>
       </c>
       <c r="C10" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1242,20 +1427,25 @@
           <t>server-a</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
-        <v>46175.52108796296</v>
+      <c r="B11" s="16" t="n">
+        <v>46176.6044212963</v>
       </c>
       <c r="C11" t="n">
         <v>1.5</v>
       </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1266,12 +1456,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1285,79 +1476,109 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Business Hours</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="n">
+      <c r="A2" s="16" t="n">
         <v>46174.99872685185</v>
       </c>
       <c r="B2" t="n">
         <v>0.12</v>
       </c>
-      <c r="C2" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="n">
-        <v>46174.99982638889</v>
+      <c r="A3" s="16" t="n">
+        <v>46175.42708333334</v>
       </c>
       <c r="B3" t="n">
         <v>0.095</v>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
-        <v>46175.00173611111</v>
+      <c r="A4" s="16" t="n">
+        <v>46176.00173611111</v>
       </c>
       <c r="B4" t="n">
         <v>2.1</v>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
-        <v>46175.34375</v>
+      <c r="A5" s="16" t="n">
+        <v>46176.34375</v>
       </c>
       <c r="B5" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
-        <v>46175.52108796296</v>
+      <c r="A6" s="16" t="n">
+        <v>46176.6044212963</v>
       </c>
       <c r="B6" t="n">
         <v>1.5</v>
       </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1368,12 +1589,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,79 +1609,109 @@
           <t>Seconds</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Business Hours</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="n">
+      <c r="A2" s="16" t="n">
         <v>46174.58334490741</v>
       </c>
       <c r="B2" t="n">
         <v>0.3</v>
       </c>
-      <c r="C2" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="n">
+      <c r="A3" s="16" t="n">
         <v>46174.76539351852</v>
       </c>
       <c r="B3" t="n">
         <v>0.175</v>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="16" t="n">
         <v>46174.99305555555</v>
       </c>
       <c r="B4" t="n">
         <v>0.09</v>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
-        <v>46175.00361111111</v>
+      <c r="A5" s="16" t="n">
+        <v>46175.46194444445</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
-        <v>46175.25</v>
+      <c r="A6" s="16" t="n">
+        <v>46176.25</v>
       </c>
       <c r="B6" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>&lt;=10s</t>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>&lt;=10s</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>